--- a/data/trans_orig/P32B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>908</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428531</t>
+          <t>428189</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438407</t>
+          <t>438402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>610223</t>
+          <t>608997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>619016</t>
+          <t>619017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14248</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>570929</t>
+          <t>571096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579977</t>
+          <t>579997</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271190</t>
+          <t>269689</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>846161</t>
+          <t>846053</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857337</t>
+          <t>857416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>770</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322615</t>
+          <t>322858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329281</t>
+          <t>329282</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128511</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130349</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>452972</t>
+          <t>453201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459628</t>
+          <t>459632</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13921</t>
+          <t>14064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>516713</t>
+          <t>518055</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>527763</t>
+          <t>527762</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291134</t>
+          <t>290991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302086</t>
+          <t>302069</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814623</t>
+          <t>814758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>828346</t>
+          <t>828089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24749</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18108</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>16469</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>36675</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16261</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>15956</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>35383</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1855169</t>
+          <t>1855208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1871384</t>
+          <t>1870699</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>876412</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>889937</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2737764</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2757970</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>878259</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>890459</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2739056</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2758483</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412479</t>
+          <t>412415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423951</t>
+          <t>423789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588549</t>
+          <t>588428</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>599328</t>
+          <t>598967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>22756</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24010</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571866</t>
+          <t>572688</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588934</t>
+          <t>589016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289321</t>
+          <t>289475</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>867894</t>
+          <t>866139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883700</t>
+          <t>883671</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436694</t>
+          <t>437334</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453608</t>
+          <t>453042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201025</t>
+          <t>201688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642113</t>
+          <t>642584</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>659216</t>
+          <t>658967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16506</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37772</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1126</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9718</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>43089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521272</t>
+          <t>521685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>542538</t>
+          <t>543196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360466</t>
+          <t>359569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369058</t>
+          <t>369051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>887023</t>
+          <t>886140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>909240</t>
+          <t>909632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43502</t>
+          <t>44262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74590</t>
+          <t>77238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50990</t>
+          <t>49859</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84477</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1967654</t>
+          <t>1965006</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1998742</t>
+          <t>1997982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1034300</t>
+          <t>1034215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1045694</t>
+          <t>1045620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3006503</t>
+          <t>3008285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3039990</t>
+          <t>3041121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>13695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416135</t>
+          <t>417524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427029</t>
+          <t>427777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180537</t>
+          <t>181326</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>599886</t>
+          <t>600728</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611395</t>
+          <t>611488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>6496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>545916</t>
+          <t>545420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564174</t>
+          <t>564123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313893</t>
+          <t>315820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866399</t>
+          <t>864983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884964</t>
+          <t>884631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>412164</t>
+          <t>413677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422853</t>
+          <t>422854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>227655</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642395</t>
+          <t>641365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652525</t>
+          <t>652524</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23634</t>
+          <t>24533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34876</t>
+          <t>33940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>550796</t>
+          <t>549897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>566344</t>
+          <t>565835</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391637</t>
+          <t>391567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>403921</t>
+          <t>404104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>947624</t>
+          <t>948560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>966985</t>
+          <t>967589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>30208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57266</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>19812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>69369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1945348</t>
+          <t>1943860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1971990</t>
+          <t>1972406</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1125470</t>
+          <t>1124933</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1138781</t>
+          <t>1138266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3076164</t>
+          <t>3077990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3107528</t>
+          <t>3106429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023</t>
+          <t>Población según si se han sentido mal o culpables por su forma de beber en 2023 (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>326609</t>
+          <t>327162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332344</t>
+          <t>332866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155105</t>
+          <t>155183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485621</t>
+          <t>485431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491842</t>
+          <t>491830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30160</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>452027</t>
+          <t>450958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470181</t>
+          <t>470362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>189042</t>
+          <t>188564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198663</t>
+          <t>198594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647391</t>
+          <t>646784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>667235</t>
+          <t>666811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16282</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317268</t>
+          <t>316948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324858</t>
+          <t>324864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361376</t>
+          <t>361457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375885</t>
+          <t>375938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685163</t>
+          <t>685354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699895</t>
+          <t>699771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7211</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24061</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>7141</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9786</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27952</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418613</t>
+          <t>419406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435463</t>
+          <t>435502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282360</t>
+          <t>281716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287642</t>
+          <t>287846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703580</t>
+          <t>703894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721746</t>
+          <t>721735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20826</t>
+          <t>21348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>48429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,47 +7961,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13525</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>23663</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>13525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6984</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>24659</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1531526</t>
+          <t>1529215</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1556818</t>
+          <t>1556296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,47 +8074,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1012322</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1002184</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1019922</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1012322</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1001188</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1018863</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2542255</t>
+          <t>2541718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2573538</t>
+          <t>2574198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32B-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>428189</t>
+          <t>429239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>438402</t>
+          <t>438414</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>608997</t>
+          <t>607886</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>619017</t>
+          <t>619010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>571096</t>
+          <t>571222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579997</t>
+          <t>579990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>269689</t>
+          <t>271710</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>846053</t>
+          <t>846907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>857416</t>
+          <t>857430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322858</t>
+          <t>322762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329282</t>
+          <t>330052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453201</t>
+          <t>452789</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>459632</t>
+          <t>460401</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>894</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>14166</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>518055</t>
+          <t>518373</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>527762</t>
+          <t>527755</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>290991</t>
+          <t>290889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302069</t>
+          <t>302060</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814758</t>
+          <t>813586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>828089</t>
+          <t>827630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,82 +2120,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9331</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17607</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>24674</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>16605</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>36431</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>9331</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>18108</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>24674</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>16469</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>36675</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1855208</t>
+          <t>1855499</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1870699</t>
+          <t>1871485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>885189</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>876913</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>889594</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2695</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2749765</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>2738008</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>2757834</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>885189</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>876412</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>889937</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>97,98%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2749765</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>2737764</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>2757970</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15113</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412415</t>
+          <t>412417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423789</t>
+          <t>423536</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>588428</t>
+          <t>587839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>598967</t>
+          <t>599056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>23516</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>572688</t>
+          <t>571928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>589016</t>
+          <t>589135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289475</t>
+          <t>289400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866139</t>
+          <t>866898</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>883671</t>
+          <t>883708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23722</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437334</t>
+          <t>437752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>453042</t>
+          <t>453327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>201688</t>
+          <t>201637</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642584</t>
+          <t>643749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658967</t>
+          <t>658609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15848</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43089</t>
+          <t>41629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>521685</t>
+          <t>520410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>543196</t>
+          <t>542793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>359569</t>
+          <t>360309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369051</t>
+          <t>369156</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>886140</t>
+          <t>887600</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>909632</t>
+          <t>909682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44262</t>
+          <t>42163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77238</t>
+          <t>75862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14522</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49859</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82695</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1965006</t>
+          <t>1966382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1997982</t>
+          <t>2000081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1034215</t>
+          <t>1033964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1045620</t>
+          <t>1045635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3008285</t>
+          <t>3006629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3041121</t>
+          <t>3040777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,39 +4642,39 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4991</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417524</t>
+          <t>416928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427777</t>
+          <t>427614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,42 +4755,42 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>183870</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>179702</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>184693</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>183870</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>181326</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>184693</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>600728</t>
+          <t>600614</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611488</t>
+          <t>611349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>11851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>545420</t>
+          <t>546613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>564123</t>
+          <t>564323</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315820</t>
+          <t>315204</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>864983</t>
+          <t>866431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884631</t>
+          <t>885019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>413677</t>
+          <t>413695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>422854</t>
+          <t>422857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>641365</t>
+          <t>643396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652524</t>
+          <t>652517</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8595</t>
+          <t>8609</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24533</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>16285</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33940</t>
+          <t>33936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549897</t>
+          <t>551346</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>565835</t>
+          <t>565821</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391567</t>
+          <t>391785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>404104</t>
+          <t>403349</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>948560</t>
+          <t>948564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>967589</t>
+          <t>967256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58754</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19812</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>40959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69369</t>
+          <t>69605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1943860</t>
+          <t>1944884</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1972406</t>
+          <t>1971385</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1124933</t>
+          <t>1124430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1138266</t>
+          <t>1138533</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3077990</t>
+          <t>3077754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3106429</t>
+          <t>3106400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,67 +6569,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5925</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5704</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4914</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -6682,69 +6682,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>330922</t>
+          <t>351187</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>327162</t>
+          <t>347230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>352606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>171764</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>168387</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>173082</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,24%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>158790</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>155183</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>160097</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>601</t>
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>489712</t>
+          <t>522951</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>485431</t>
+          <t>519040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>491830</t>
+          <t>525241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,81%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332866</t>
+          <t>353155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160097</t>
+          <t>173082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>492963</t>
+          <t>526237</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25798</t>
+          <t>22665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>5696</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18020</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>464104</t>
+          <t>488385</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450958</t>
+          <t>478058</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470362</t>
+          <t>494775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>195427</t>
+          <t>216822</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188564</t>
+          <t>209696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>198594</t>
+          <t>220266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>659531</t>
+          <t>705207</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646784</t>
+          <t>693205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>666811</t>
+          <t>712882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>476756</t>
+          <t>500723</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>200795</t>
+          <t>222518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>200795</t>
+          <t>222518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200795</t>
+          <t>222518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>677551</t>
+          <t>723241</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>677551</t>
+          <t>723241</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>677551</t>
+          <t>723241</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>11458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>22866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>322669</t>
+          <t>353555</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316948</t>
+          <t>344345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324864</t>
+          <t>357937</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>372249</t>
+          <t>196304</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>361457</t>
+          <t>187859</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>375938</t>
+          <t>199708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>694918</t>
+          <t>549859</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>685354</t>
+          <t>538451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699771</t>
+          <t>556146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>325348</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>701445</t>
+          <t>561317</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>25431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>20733</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27638</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>429002</t>
+          <t>449091</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>419406</t>
+          <t>439092</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>435502</t>
+          <t>455873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>285856</t>
+          <t>302542</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281716</t>
+          <t>294380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>287846</t>
+          <t>305832</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>714859</t>
+          <t>751633</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703894</t>
+          <t>739110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721735</t>
+          <t>759779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>442674</t>
+          <t>464523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288857</t>
+          <t>307843</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>731532</t>
+          <t>772366</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>29995</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>53510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>74234</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1546697</t>
+          <t>1642218</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1529215</t>
+          <t>1625235</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1556296</t>
+          <t>1653389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1012322</t>
+          <t>887432</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1002184</t>
+          <t>874581</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1019922</t>
+          <t>894420</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2559019</t>
+          <t>2529650</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2541718</t>
+          <t>2508926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2574198</t>
+          <t>2542994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1577644</t>
+          <t>1678584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1025847</t>
+          <t>904576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2603491</t>
+          <t>2583160</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
